--- a/ParallelLSTM/result/data/검증데이터/검증데이터36/250716_1700.xlsx
+++ b/ParallelLSTM/result/data/검증데이터/검증데이터36/250716_1700.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magpie\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magpie\Downloads\AI 시뮬레이터 모델\자료\성남시 탄천 수위 예측 학습 자료 (성능개선)\검증데이터\검증데이터36\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAD01D0-D6CF-488B-AA7F-4C31E631E4B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input2" sheetId="1" r:id="rId1"/>
@@ -57,18 +58,18 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>성남시(궁내교)_FW</t>
+    <t>성남시(궁내교)_Q</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>서울시(대곡교)_FW</t>
+    <t>서울시(대곡교)_Q</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -996,7 +997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
